--- a/survey_templates/036_pre_class_survey--survey_templates.xlsx
+++ b/survey_templates/036_pre_class_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,97 +600,28 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>student_feedback</t>
+          <t>classroom_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Student Feedback</t>
+          <t>Classroom Experience</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>expectations</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Expectations</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>lessons</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Lessons</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>knowledge_gaps</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Knowledge Gaps</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +638,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>before_the_course_began,_i_had_the_following_expectations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Before the course began, I had the following expectations</t>
         </is>
       </c>
     </row>
@@ -757,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>mostly_met,_some_not_met</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Mostly met, some not met</t>
         </is>
       </c>
     </row>
@@ -774,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>not_at_all_met</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Not at all met</t>
         </is>
       </c>
     </row>
@@ -791,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>what_did_you_learn_from_this_course?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>What did you learn from this course?</t>
         </is>
       </c>
     </row>
@@ -808,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>what_lessons_did_you_not_understand_or_need_further_clarification_on?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>What lessons did you not understand or need further clarification on?</t>
         </is>
       </c>
     </row>
@@ -825,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
@@ -842,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>what_knowledge_gaps_did_you_identify_during_the_course?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>What knowledge gaps did you identify during the course?</t>
         </is>
       </c>
     </row>
@@ -859,182 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>how_would_you_address_these_knowledge_gaps_in_future_courses?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>knowledge_gaps_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>expectations_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>expectations_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>expectations_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>lessons_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>lessons_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>lessons_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>knowledge_gaps_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>knowledge_gaps_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>knowledge_gaps_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>option3</t>
+          <t>How would you address these knowledge gaps in future courses?</t>
         </is>
       </c>
     </row>
